--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_04/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_04/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999996610936</v>
+        <v>31.80642995897011</v>
       </c>
       <c r="B2" t="n">
-        <v>99.57255921397064</v>
+        <v>62.82985537838879</v>
       </c>
       <c r="C2" t="n">
-        <v>38.78076145576239</v>
+        <v>38.57278921674467</v>
       </c>
       <c r="D2" t="n">
-        <v>6.117232657098676</v>
+        <v>5.849585006547325</v>
       </c>
       <c r="E2" t="n">
-        <v>4.900196189292259</v>
+        <v>2.19572770971801</v>
       </c>
       <c r="F2" t="n">
-        <v>7.763217807632933</v>
+        <v>1.902570534085073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00371770950698454</v>
+        <v>0.199184200410489</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9684337866529584</v>
+        <v>-4.49952331365542e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9750421315302151</v>
+        <v>-0.3983698063030873</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9937351412844053</v>
+        <v>-0.4214686263568848</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001013024818479311</v>
+        <v>-0.003705616751319009</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069727408706</v>
+        <v>-0.6362901872435632</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0002766561755271818</v>
+        <v>-0.0003174839070906044</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30.40981315613967</v>
+        <v>31.80642995897011</v>
       </c>
       <c r="B3" t="n">
-        <v>71.34222705156091</v>
+        <v>62.63011018869831</v>
       </c>
       <c r="C3" t="n">
-        <v>38.77987645575738</v>
+        <v>38.57278921674467</v>
       </c>
       <c r="D3" t="n">
-        <v>6.03109023750347</v>
+        <v>5.849585006547325</v>
       </c>
       <c r="E3" t="n">
-        <v>2.394784524272573</v>
+        <v>2.227956386075017</v>
       </c>
       <c r="F3" t="n">
-        <v>1.817437055535568</v>
+        <v>1.902570534085073</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2423987001062228</v>
+        <v>0.199184200410489</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0007605167248810103</v>
+        <v>-4.49952331365542e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3987073749044466</v>
+        <v>-0.3983698063030873</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4200625000221787</v>
+        <v>-0.4214686263568848</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.004236399174920178</v>
+        <v>-0.003705616751319009</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6268028539590174</v>
+        <v>-0.6362901872435632</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.636717093279753e-05</v>
+        <v>-0.0003174839070906044</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30.40981315613967</v>
+        <v>99.99999999711355</v>
       </c>
       <c r="B4" t="n">
-        <v>71.33829201472297</v>
+        <v>79.61669856232734</v>
       </c>
       <c r="C4" t="n">
-        <v>38.77987645575738</v>
+        <v>38.57242499831867</v>
       </c>
       <c r="D4" t="n">
-        <v>6.03109023750347</v>
+        <v>6.795212861811825</v>
       </c>
       <c r="E4" t="n">
-        <v>2.24948754173535</v>
+        <v>2.597270660769426</v>
       </c>
       <c r="F4" t="n">
-        <v>1.817437055535568</v>
+        <v>7.89422316131749</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2423987001062228</v>
+        <v>0.003666108523182342</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0007605167248810103</v>
+        <v>-0.9640905238283217</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3987073749044466</v>
+        <v>-0.9716452453925631</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4200625000221787</v>
+        <v>-0.9926066475818146</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.004236399174920178</v>
+        <v>-0.001758299608249985</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6268028539590174</v>
+        <v>-0.5874999999794339</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.636717093279753e-05</v>
+        <v>-0.0002324996076884245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50.16301132076924</v>
+        <v>91.7805341863619</v>
       </c>
       <c r="B5" t="n">
-        <v>102.6383576742586</v>
+        <v>118.1808178224384</v>
       </c>
       <c r="C5" t="n">
-        <v>38.77970826070565</v>
+        <v>38.57267058429078</v>
       </c>
       <c r="D5" t="n">
-        <v>7.141908796321155</v>
+        <v>8.12232805186291</v>
       </c>
       <c r="E5" t="n">
-        <v>4.985673588501332</v>
+        <v>2.771158554064164</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2257079457878</v>
+        <v>6.941233582538614</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03780942921387086</v>
+        <v>0.004831236855545013</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7720223002516288</v>
+        <v>-0.9542228612657699</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8252045229612937</v>
+        <v>-0.96416825711744</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9176497294735835</v>
+        <v>-0.9898684826403144</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.08012726587243919</v>
+        <v>-0.08260663924481693</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5830855043821634</v>
+        <v>-0.5289363060778285</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.210308247867614e-05</v>
+        <v>-0.0002898030011840025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47.40673556481001</v>
+        <v>83.67064708822565</v>
       </c>
       <c r="B6" t="n">
-        <v>76.8173978275918</v>
+        <v>95.82757640802713</v>
       </c>
       <c r="C6" t="n">
-        <v>38.78439932148179</v>
+        <v>38.57257513007524</v>
       </c>
       <c r="D6" t="n">
-        <v>7.453191499921204</v>
+        <v>8.73896381070352</v>
       </c>
       <c r="E6" t="n">
-        <v>4.80005061075985</v>
+        <v>2.125678622767483</v>
       </c>
       <c r="F6" t="n">
-        <v>3.012204185283834</v>
+        <v>6.010373453680536</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04667924733792787</v>
+        <v>0.006548604449834624</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7306209036220458</v>
+        <v>-0.9403990313586843</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7969135971616544</v>
+        <v>-0.954221877647738</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8973337621039943</v>
+        <v>-0.9857175779680959</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07480325541113444</v>
+        <v>-0.02106416265209475</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5647836625226439</v>
+        <v>-0.4711533605036078</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001017749040711366</v>
+        <v>-0.0002675303508894999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34.22313561065583</v>
+        <v>73.75231016699922</v>
       </c>
       <c r="B7" t="n">
-        <v>64.03167777788313</v>
+        <v>113.2824350298291</v>
       </c>
       <c r="C7" t="n">
-        <v>38.78075312172312</v>
+        <v>38.57286401074359</v>
       </c>
       <c r="D7" t="n">
-        <v>5.824316518676959</v>
+        <v>9.674150241467371</v>
       </c>
       <c r="E7" t="n">
-        <v>4.73890200945342</v>
+        <v>3.464634123390034</v>
       </c>
       <c r="F7" t="n">
-        <v>2.080450756924607</v>
+        <v>5.020340591091275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1536063229902488</v>
+        <v>0.01008076931583347</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2971483316799932</v>
+        <v>-0.914207331945502</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5454087970954412</v>
+        <v>-0.9332682099795359</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6364818089869171</v>
+        <v>-0.9770003469904455</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1033107810373441</v>
+        <v>-0.01481139396149533</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6505410078240036</v>
+        <v>-0.4004852099398695</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0002749583951490951</v>
+        <v>-0.0003349358401701086</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61.87758929031101</v>
+        <v>38.00703823625561</v>
       </c>
       <c r="B8" t="n">
-        <v>113.7411219535551</v>
+        <v>62.58872602671661</v>
       </c>
       <c r="C8" t="n">
-        <v>38.85535864641081</v>
+        <v>38.57278921674467</v>
       </c>
       <c r="D8" t="n">
-        <v>10.68472902589761</v>
+        <v>5.851713029405716</v>
       </c>
       <c r="E8" t="n">
-        <v>4.718389072238278</v>
+        <v>4.44284917609636</v>
       </c>
       <c r="F8" t="n">
-        <v>3.992987104108449</v>
+        <v>2.412810865216935</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01923037636116146</v>
+        <v>0.1008609779318909</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8747588984468199</v>
+        <v>-0.4098979388030379</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9005054178805046</v>
+        <v>-0.6052606232292195</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9621300279309649</v>
+        <v>-0.7120471567521288</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.06236479211523165</v>
+        <v>-0.1971698589996144</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3372299067192343</v>
+        <v>-0.6631667895277676</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01547332642575521</v>
+        <v>-0.0003174839070906044</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65.60683125941659</v>
+        <v>69.19228692823229</v>
       </c>
       <c r="B9" t="n">
-        <v>111.6590465838498</v>
+        <v>110.4465897350371</v>
       </c>
       <c r="C9" t="n">
-        <v>38.86598818948173</v>
+        <v>38.5721448272886</v>
       </c>
       <c r="D9" t="n">
-        <v>10.17938647277928</v>
+        <v>10.30335010989785</v>
       </c>
       <c r="E9" t="n">
-        <v>4.346134755054342</v>
+        <v>2.491696399183248</v>
       </c>
       <c r="F9" t="n">
-        <v>4.265128807779772</v>
+        <v>4.636015918335146</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01553198001450894</v>
+        <v>0.01263901900861229</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8944889446032868</v>
+        <v>-0.8966574101020788</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9166132592981401</v>
+        <v>-0.9183615711790404</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9697836639631909</v>
+        <v>-0.9706272784851525</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03329936680218974</v>
+        <v>-0.05572439273472121</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.365087604268273</v>
+        <v>-0.3679950443636552</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01763873854858965</v>
+        <v>-0.0001671263673400092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36.01229921674681</v>
+        <v>45.50448787531182</v>
       </c>
       <c r="B10" t="n">
-        <v>59.34432306960946</v>
+        <v>73.92484438624861</v>
       </c>
       <c r="C10" t="n">
-        <v>39.33845203320816</v>
+        <v>38.57814807715106</v>
       </c>
       <c r="D10" t="n">
-        <v>5.137400927856646</v>
+        <v>7.491324340693462</v>
       </c>
       <c r="E10" t="n">
-        <v>3.627536787735852</v>
+        <v>4.394570264306709</v>
       </c>
       <c r="F10" t="n">
-        <v>2.171253062117019</v>
+        <v>2.861904053172649</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1257813606794204</v>
+        <v>0.05324009898526057</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3964028341765654</v>
+        <v>-0.6533340901401105</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5982478405358899</v>
+        <v>-0.7470856871366148</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7031183495122159</v>
+        <v>-0.8574116494182064</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03192460521038697</v>
+        <v>-0.02900959834091382</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.659583130758495</v>
+        <v>-0.5533632525020789</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07573392300958294</v>
+        <v>-0.001567884668579878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53.24191945192531</v>
+        <v>47.49534675437499</v>
       </c>
       <c r="B11" t="n">
-        <v>69.25866113426092</v>
+        <v>79.32777342099524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.77976101092521</v>
+        <v>38.58422140488984</v>
       </c>
       <c r="D11" t="n">
-        <v>7.107242191017444</v>
+        <v>7.426208296479369</v>
       </c>
       <c r="E11" t="n">
-        <v>2.408902937232425</v>
+        <v>4.218532905133452</v>
       </c>
       <c r="F11" t="n">
-        <v>3.519337418285417</v>
+        <v>3.028632482738153</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03041215070033308</v>
+        <v>0.04539397609151608</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8086357747756544</v>
+        <v>-0.6931523431188796</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.851230501228695</v>
+        <v>-0.7721100155601038</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9346178864528161</v>
+        <v>-0.8782189522630728</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1700779014249073</v>
+        <v>-0.0006802567990489477</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6035296452104444</v>
+        <v>-0.5508038627777083</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.284916668514144e-05</v>
+        <v>-0.002984994474296149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31.87195861563368</v>
+        <v>32.31784217018323</v>
       </c>
       <c r="B12" t="n">
-        <v>72.47862065917877</v>
+        <v>62.58872602671661</v>
       </c>
       <c r="C12" t="n">
-        <v>38.78104955276682</v>
+        <v>38.57278921674467</v>
       </c>
       <c r="D12" t="n">
-        <v>5.932554034027763</v>
+        <v>5.849585006547325</v>
       </c>
       <c r="E12" t="n">
-        <v>3.633191497474477</v>
+        <v>4.44284917609636</v>
       </c>
       <c r="F12" t="n">
-        <v>1.911930631284586</v>
+        <v>1.941204979509272</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2020629369206069</v>
+        <v>0.1873244074906397</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1312796134361953</v>
+        <v>-0.04644387464544063</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4615680754826599</v>
+        <v>-0.4204314166848521</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5184468681877274</v>
+        <v>-0.4568316099825083</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.03412719614331883</v>
+        <v>-0.02664596543524831</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6359047944071308</v>
+        <v>-0.6394865135636452</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.000335346256726284</v>
+        <v>-0.0003174839070906044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78.30315284506722</v>
+        <v>36.36966669456257</v>
       </c>
       <c r="B13" t="n">
-        <v>164.6725068457459</v>
+        <v>58.25468362696428</v>
       </c>
       <c r="C13" t="n">
-        <v>38.79599753635031</v>
+        <v>38.58448150464958</v>
       </c>
       <c r="D13" t="n">
-        <v>9.196303830983066</v>
+        <v>5.391653245734425</v>
       </c>
       <c r="E13" t="n">
-        <v>2.37315702660967</v>
+        <v>4.082464392878773</v>
       </c>
       <c r="F13" t="n">
-        <v>5.424912971005915</v>
+        <v>2.213638815916564</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008350170095209431</v>
+        <v>0.118853412548713</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9367919963445855</v>
+        <v>-0.3292277016054684</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.951686614400802</v>
+        <v>-0.5622694815598984</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9845568268045944</v>
+        <v>-0.6594806865351583</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.08869688260670845</v>
+        <v>-0.02070357703519014</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4599300118268301</v>
+        <v>-0.6179526656066224</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.003380495483521609</v>
+        <v>-0.003045684418236105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83.72917034311391</v>
+        <v>93.73035342329381</v>
       </c>
       <c r="B14" t="n">
-        <v>125.2376181619886</v>
+        <v>109.5890631142939</v>
       </c>
       <c r="C14" t="n">
-        <v>39.03074660958502</v>
+        <v>38.57234565751215</v>
       </c>
       <c r="D14" t="n">
-        <v>9.749137285391667</v>
+        <v>8.358055238097515</v>
       </c>
       <c r="E14" t="n">
-        <v>4.526302083376661</v>
+        <v>3.734400725441964</v>
       </c>
       <c r="F14" t="n">
-        <v>6.116507672326422</v>
+        <v>7.225546442618397</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00670048361341287</v>
+        <v>0.004523466573479273</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9477484492457632</v>
+        <v>-0.9568481523317102</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9593605079602857</v>
+        <v>-0.9660949027216659</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9879386756095879</v>
+        <v>-0.990612997991404</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2975621753657883</v>
+        <v>-0.1824575540155961</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5004627408931154</v>
+        <v>-0.5428287681409683</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.05095607516587444</v>
+        <v>-0.0002139867528364037</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>35.12237229637367</v>
+        <v>49.95413453209191</v>
       </c>
       <c r="B15" t="n">
-        <v>59.34432306960946</v>
+        <v>72.554978495464</v>
       </c>
       <c r="C15" t="n">
-        <v>38.79523129597859</v>
+        <v>38.57302399282172</v>
       </c>
       <c r="D15" t="n">
-        <v>5.388864404235014</v>
+        <v>7.163801056587516</v>
       </c>
       <c r="E15" t="n">
-        <v>4.925907150107304</v>
+        <v>4.488268370344393</v>
       </c>
       <c r="F15" t="n">
-        <v>2.166052702484751</v>
+        <v>3.2223115849284</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1382170426352306</v>
+        <v>0.03761684236712282</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3499442930715819</v>
+        <v>-0.7357053832929296</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5733093820887469</v>
+        <v>-0.8002377964336495</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6725049385185261</v>
+        <v>-0.9000381038295836</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2094925288485403</v>
+        <v>-0.0005355391791127556</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6481239371911361</v>
+        <v>-0.5663761853699154</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.003224399762486833</v>
+        <v>-0.0003722649917339838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36.72800023738684</v>
+        <v>50.66187453727906</v>
       </c>
       <c r="B16" t="n">
-        <v>58.62955664483039</v>
+        <v>79.32777342099524</v>
       </c>
       <c r="C16" t="n">
-        <v>38.78263513803982</v>
+        <v>38.58422140488984</v>
       </c>
       <c r="D16" t="n">
-        <v>5.155597421543217</v>
+        <v>7.4401956873013</v>
       </c>
       <c r="E16" t="n">
-        <v>3.482956599783035</v>
+        <v>2.737934727508418</v>
       </c>
       <c r="F16" t="n">
-        <v>2.226119278955055</v>
+        <v>3.323271171144189</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1166684535660305</v>
+        <v>0.03579863422542488</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4306895727713274</v>
+        <v>-0.7463456077548207</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6170071747057162</v>
+        <v>-0.8074035391393917</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7252673400410986</v>
+        <v>-0.9052882653798972</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.06584944024405735</v>
+        <v>-0.09347583430746359</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6619265782899297</v>
+        <v>-0.5708585387361007</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0006583559617560047</v>
+        <v>-0.002984994474296149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94.7653486840918</v>
+        <v>35.71828103632093</v>
       </c>
       <c r="B17" t="n">
-        <v>141.1519709557368</v>
+        <v>58.57295912175508</v>
       </c>
       <c r="C17" t="n">
-        <v>38.79295202676581</v>
+        <v>38.57314492146746</v>
       </c>
       <c r="D17" t="n">
-        <v>8.473163269341626</v>
+        <v>5.454613277983339</v>
       </c>
       <c r="E17" t="n">
-        <v>4.365911214248356</v>
+        <v>2.831733864060906</v>
       </c>
       <c r="F17" t="n">
-        <v>7.33567178634307</v>
+        <v>2.165776285545157</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004447956751483816</v>
+        <v>0.1273683799112666</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9632319376523438</v>
+        <v>-0.2921785366625823</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.970914516516212</v>
+        <v>-0.5428622853515453</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.99236033777045</v>
+        <v>-0.6343088412671908</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3457933545073075</v>
+        <v>-0.05617122722712478</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5829037626522777</v>
+        <v>-0.6069870395834841</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.002760075270679795</v>
+        <v>-0.0004004816757410823</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33.29141514732499</v>
+        <v>34.67240308385186</v>
       </c>
       <c r="B18" t="n">
-        <v>79.53654946627914</v>
+        <v>58.89768864756557</v>
       </c>
       <c r="C18" t="n">
-        <v>38.78744662378396</v>
+        <v>39.56477056736446</v>
       </c>
       <c r="D18" t="n">
-        <v>5.673702014380147</v>
+        <v>5.391517850285409</v>
       </c>
       <c r="E18" t="n">
-        <v>4.75048972157628</v>
+        <v>3.138313671953355</v>
       </c>
       <c r="F18" t="n">
-        <v>1.988626244736819</v>
+        <v>2.088219311905732</v>
       </c>
       <c r="G18" t="n">
-        <v>0.170570549246117</v>
+        <v>0.1427337506988531</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2371479359693195</v>
+        <v>-0.2267341459893199</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5145359320258908</v>
+        <v>-0.5092478469976586</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5948139552241372</v>
+        <v>-0.5887858196879476</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01130514577044091</v>
+        <v>-0.004221763701123987</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.644740993799092</v>
+        <v>-0.6477762797297776</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.001638534459524249</v>
+        <v>-0.231779799051707</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41.6422547846459</v>
+        <v>87.62600916926361</v>
       </c>
       <c r="B19" t="n">
-        <v>72.50402079156197</v>
+        <v>79.20593768284921</v>
       </c>
       <c r="C19" t="n">
-        <v>38.78553663181611</v>
+        <v>38.57313202281141</v>
       </c>
       <c r="D19" t="n">
-        <v>5.034425623238298</v>
+        <v>8.401747396508531</v>
       </c>
       <c r="E19" t="n">
-        <v>4.56553767532165</v>
+        <v>4.431785783824606</v>
       </c>
       <c r="F19" t="n">
-        <v>2.642364327122901</v>
+        <v>6.44834019554517</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07266020805359817</v>
+        <v>0.005617920270119526</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.607588893018105</v>
+        <v>-0.9477772559401909</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7191856305068192</v>
+        <v>-0.9594693778318668</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.832114719667078</v>
+        <v>-0.9879766656728267</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2452265646180978</v>
+        <v>-0.03933676643821666</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6967254557943731</v>
+        <v>-0.4993353153310032</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.001249437794303699</v>
+        <v>-0.0003974719893298784</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>34.81703091301628</v>
+        <v>96.61329605391886</v>
       </c>
       <c r="B20" t="n">
-        <v>68.03961715011293</v>
+        <v>100.2214732795392</v>
       </c>
       <c r="C20" t="n">
-        <v>39.08274339308046</v>
+        <v>39.67599962734285</v>
       </c>
       <c r="D20" t="n">
-        <v>5.411859327548208</v>
+        <v>7.293403887584176</v>
       </c>
       <c r="E20" t="n">
-        <v>4.926663573505735</v>
+        <v>3.679736960764379</v>
       </c>
       <c r="F20" t="n">
-        <v>2.083210567609224</v>
+        <v>7.509432211335767</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1434517361474572</v>
+        <v>0.00409401412058136</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3324599975819284</v>
+        <v>-0.9604183839378403</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5639756035181652</v>
+        <v>-0.9688180764436054</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6606090350081448</v>
+        <v>-0.9916113723725238</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0001827143762149939</v>
+        <v>-0.0488044633120563</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6542380405914339</v>
+        <v>-0.5633697343841718</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.05858769469157208</v>
+        <v>-0.2577332463799971</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>93.70035408376428</v>
+        <v>38.9761400763514</v>
       </c>
       <c r="B21" t="n">
-        <v>114.484085336276</v>
+        <v>62.91738296729596</v>
       </c>
       <c r="C21" t="n">
-        <v>38.78221385473442</v>
+        <v>38.57264686874303</v>
       </c>
       <c r="D21" t="n">
-        <v>7.027848886348223</v>
+        <v>5.243134578711528</v>
       </c>
       <c r="E21" t="n">
-        <v>2.404733956936811</v>
+        <v>2.881719208797182</v>
       </c>
       <c r="F21" t="n">
-        <v>7.018166114128923</v>
+        <v>2.426755026830721</v>
       </c>
       <c r="G21" t="n">
-        <v>0.004576995783519579</v>
+        <v>0.09135408544961875</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9621151303013618</v>
+        <v>-0.4527421679070866</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9701381164545287</v>
+        <v>-0.6289772949808142</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9920678808977705</v>
+        <v>-0.7395469731704007</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.009986580847723837</v>
+        <v>-0.05164858533484509</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5749481787258213</v>
+        <v>-0.6689208317033364</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0005725336483622723</v>
+        <v>-0.0002842693733731694</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>32.58130877516832</v>
+        <v>35.2201766620834</v>
       </c>
       <c r="B22" t="n">
-        <v>77.62735462413659</v>
+        <v>58.88936395503548</v>
       </c>
       <c r="C22" t="n">
-        <v>38.7851836482801</v>
+        <v>38.58497796336744</v>
       </c>
       <c r="D22" t="n">
-        <v>5.7782775316199</v>
+        <v>5.380247392241893</v>
       </c>
       <c r="E22" t="n">
-        <v>4.869010511710626</v>
+        <v>4.654097110194582</v>
       </c>
       <c r="F22" t="n">
-        <v>1.946646001531785</v>
+        <v>2.11531319335516</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1854393407137039</v>
+        <v>0.1343066560500728</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1865139925054807</v>
+        <v>-0.2620408774967218</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4889685522828492</v>
+        <v>-0.5272916155755502</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5587109441388711</v>
+        <v>-0.6135372261562466</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01433709519264309</v>
+        <v>-0.003833502088849086</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6403205403693543</v>
+        <v>-0.6264131101787473</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.001177529263248172</v>
+        <v>-0.003161524785737363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97.82636604572143</v>
+        <v>60.72526769827395</v>
       </c>
       <c r="B23" t="n">
-        <v>71.21311090482246</v>
+        <v>102.2430384554667</v>
       </c>
       <c r="C23" t="n">
-        <v>38.78074727060437</v>
+        <v>38.57244029767573</v>
       </c>
       <c r="D23" t="n">
-        <v>6.457241251002051</v>
+        <v>10.52251646595096</v>
       </c>
       <c r="E23" t="n">
-        <v>4.99304064478116</v>
+        <v>2.98796255724322</v>
       </c>
       <c r="F23" t="n">
-        <v>7.502989982894008</v>
+        <v>3.885100534635354</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003986138521233435</v>
+        <v>0.02012286760262979</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9664334308655006</v>
+        <v>-0.8504528516581257</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.973473545585538</v>
+        <v>-0.8821031818728156</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9932175732045122</v>
+        <v>-0.9526523220493562</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.008166025543551539</v>
+        <v>-0.01087348173184339</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6057697757882092</v>
+        <v>-0.3304395077370547</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0002737664263700756</v>
+        <v>-0.0002360694576684919</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>30.86140595887251</v>
+        <v>79.92995758782347</v>
       </c>
       <c r="B24" t="n">
-        <v>63.55035794253567</v>
+        <v>115.7075984578253</v>
       </c>
       <c r="C24" t="n">
-        <v>38.78546747749949</v>
+        <v>38.57286349599188</v>
       </c>
       <c r="D24" t="n">
-        <v>5.051916864724258</v>
+        <v>9.672792796145425</v>
       </c>
       <c r="E24" t="n">
-        <v>4.89907147940824</v>
+        <v>4.581862922647955</v>
       </c>
       <c r="F24" t="n">
-        <v>1.826165765715378</v>
+        <v>5.691263324657188</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2259266916337084</v>
+        <v>0.007672519855354959</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.04566692532334824</v>
+        <v>-0.9319556709167423</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4203442934674902</v>
+        <v>-0.9483183521286638</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4553268651596705</v>
+        <v>-0.9830093125228164</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.04725738619165872</v>
+        <v>-0.1304696019629507</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6749958681568698</v>
+        <v>-0.4445009478132422</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.001235349926693818</v>
+        <v>-0.0003348157314396472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>33.47097208100232</v>
+        <v>41.53456892121839</v>
       </c>
       <c r="B25" t="n">
-        <v>72.55982587437218</v>
+        <v>58.88936395503548</v>
       </c>
       <c r="C25" t="n">
-        <v>38.781110719958</v>
+        <v>38.57417969718738</v>
       </c>
       <c r="D25" t="n">
-        <v>5.854343501404824</v>
+        <v>5.377914173311217</v>
       </c>
       <c r="E25" t="n">
-        <v>4.730744064082414</v>
+        <v>4.654097110194582</v>
       </c>
       <c r="F25" t="n">
-        <v>2.024576628050173</v>
+        <v>2.685822786235747</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1673004857240629</v>
+        <v>0.07199186848254753</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2491050913687052</v>
+        <v>-0.5467029679986108</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5206122702463666</v>
+        <v>-0.6826406902687754</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6031525213784517</v>
+        <v>-0.7970173566709658</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.07911673637675783</v>
+        <v>-0.2274966185803033</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6458587461449786</v>
+        <v>-0.6841115029697342</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0003478070159919161</v>
+        <v>-0.0006419293437230633</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40.61328114777395</v>
+        <v>32.87979969891678</v>
       </c>
       <c r="B26" t="n">
-        <v>71.08440481377839</v>
+        <v>62.91738296729596</v>
       </c>
       <c r="C26" t="n">
-        <v>38.78445133384641</v>
+        <v>38.57265916055643</v>
       </c>
       <c r="D26" t="n">
-        <v>5.108871862216018</v>
+        <v>5.833326293002583</v>
       </c>
       <c r="E26" t="n">
-        <v>4.448308279181468</v>
+        <v>2.881719208797182</v>
       </c>
       <c r="F26" t="n">
-        <v>2.552451979390521</v>
+        <v>1.982390573363524</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07984451820454974</v>
+        <v>0.1752949711775791</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5773977529380205</v>
+        <v>-0.09417164618368264</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7009998758879151</v>
+        <v>-0.4434433636867284</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8148112404569491</v>
+        <v>-0.4926238127219655</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2071134704913011</v>
+        <v>-0.00948681150793915</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.690320035112953</v>
+        <v>-0.637861279415274</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.001028344811774267</v>
+        <v>-0.0002871374631670254</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>38.30680906899772</v>
+        <v>43.56185334623383</v>
       </c>
       <c r="B27" t="n">
-        <v>70.60024599864575</v>
+        <v>76.83726646211369</v>
       </c>
       <c r="C27" t="n">
-        <v>38.78442384052259</v>
+        <v>38.57281352695829</v>
       </c>
       <c r="D27" t="n">
-        <v>5.051916864724258</v>
+        <v>7.865741034414647</v>
       </c>
       <c r="E27" t="n">
-        <v>4.535151319825685</v>
+        <v>2.170616184203969</v>
       </c>
       <c r="F27" t="n">
-        <v>2.332628698229604</v>
+        <v>2.74420076650686</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09949725675771952</v>
+        <v>0.06285678120470242</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4974919251426243</v>
+        <v>-0.6054283883994002</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6544398781418889</v>
+        <v>-0.7174521391629478</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.767116659718602</v>
+        <v>-0.8307419345142495</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.05184091936836129</v>
+        <v>-0.03864682388617258</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6759621123974373</v>
+        <v>-0.53315204675052</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.001022743971146754</v>
+        <v>-0.0003231562902686336</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>32.58360548732298</v>
+        <v>87.3863600622233</v>
       </c>
       <c r="B28" t="n">
-        <v>79.45610777778158</v>
+        <v>65.78748471762107</v>
       </c>
       <c r="C28" t="n">
-        <v>38.7851836482801</v>
+        <v>38.57658415789373</v>
       </c>
       <c r="D28" t="n">
-        <v>5.778982417444632</v>
+        <v>8.266532107195685</v>
       </c>
       <c r="E28" t="n">
-        <v>3.600885590779768</v>
+        <v>4.431785783824606</v>
       </c>
       <c r="F28" t="n">
-        <v>1.946907057125664</v>
+        <v>6.402353964113969</v>
       </c>
       <c r="G28" t="n">
-        <v>0.185390034775533</v>
+        <v>0.005663706680523397</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1866839601068497</v>
+        <v>-0.9478254634454456</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4890534728430078</v>
+        <v>-0.9599502077508559</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5588329918929003</v>
+        <v>-0.9880604014956221</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.01468176568797151</v>
+        <v>-0.1196307150166941</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.6403348375359749</v>
+        <v>-0.2132577306369906</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.001177529263248172</v>
+        <v>-0.001202970175204626</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>42.76373657856483</v>
+        <v>37.03442550253013</v>
       </c>
       <c r="B29" t="n">
-        <v>71.50576173222008</v>
+        <v>58.57295912175508</v>
       </c>
       <c r="C29" t="n">
-        <v>38.78223139888077</v>
+        <v>38.57314492146746</v>
       </c>
       <c r="D29" t="n">
-        <v>5.034425623238298</v>
+        <v>5.715488871262209</v>
       </c>
       <c r="E29" t="n">
-        <v>4.705105059541301</v>
+        <v>2.831733864060906</v>
       </c>
       <c r="F29" t="n">
-        <v>2.737920943725448</v>
+        <v>2.310280511018763</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06582805604233688</v>
+        <v>0.1111832185670419</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6372118692745838</v>
+        <v>-0.3627579311736331</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.737365849911526</v>
+        <v>-0.5797863321475154</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8486520872002856</v>
+        <v>-0.6812072211830706</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2566572805907427</v>
+        <v>-0.115099821035356</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6980655560937541</v>
+        <v>-0.6573919014212726</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.000576107678493142</v>
+        <v>-0.0004004816757410823</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>59.17402592782946</v>
+        <v>41.40833610430956</v>
       </c>
       <c r="B30" t="n">
-        <v>194.4222211868039</v>
+        <v>77.82422238740824</v>
       </c>
       <c r="C30" t="n">
-        <v>39.88777785304794</v>
+        <v>38.57391251727126</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80141005974179</v>
+        <v>7.92445119044844</v>
       </c>
       <c r="E30" t="n">
-        <v>4.86620857997421</v>
+        <v>3.760224182542404</v>
       </c>
       <c r="F30" t="n">
-        <v>3.812708438548573</v>
+        <v>2.578902658724216</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02268882188332601</v>
+        <v>0.07609732727480459</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8571761717238301</v>
+        <v>-0.5414445998366086</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8865837264118172</v>
+        <v>-0.6793121843119746</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.954961708560116</v>
+        <v>-0.7934831950724744</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0646194136838328</v>
+        <v>-0.02504559639915595</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3170340998821849</v>
+        <v>-0.5260555740287305</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.09027598389834106</v>
+        <v>-0.0005795873632932769</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30.86140595887251</v>
+        <v>33.57579106915227</v>
       </c>
       <c r="B31" t="n">
-        <v>63.15149540073693</v>
+        <v>60.83904230756875</v>
       </c>
       <c r="C31" t="n">
-        <v>38.78546747749949</v>
+        <v>38.57219887980479</v>
       </c>
       <c r="D31" t="n">
-        <v>5.020040214474179</v>
+        <v>5.618026358079186</v>
       </c>
       <c r="E31" t="n">
-        <v>4.89907147940824</v>
+        <v>2.631192384164434</v>
       </c>
       <c r="F31" t="n">
-        <v>1.836427200846487</v>
+        <v>2.010712614858372</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2256437424947478</v>
+        <v>0.1615117715717875</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.04584717750762467</v>
+        <v>-0.1490800853013187</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4204549707261698</v>
+        <v>-0.4703623767590192</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4555514279683693</v>
+        <v>-0.533094816574656</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.09926802389452985</v>
+        <v>-0.006016307729038614</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6819957123407416</v>
+        <v>-0.6473486941822018</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.001235349926693818</v>
+        <v>-0.0001797386211176144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>39.38928937321164</v>
+        <v>75.02917485120123</v>
       </c>
       <c r="B32" t="n">
-        <v>72.40042008332554</v>
+        <v>113.2824350298291</v>
       </c>
       <c r="C32" t="n">
-        <v>38.79209389036737</v>
+        <v>38.57286401074359</v>
       </c>
       <c r="D32" t="n">
-        <v>5.048433638843806</v>
+        <v>10.7137834618953</v>
       </c>
       <c r="E32" t="n">
-        <v>4.28354834099957</v>
+        <v>4.090838635103147</v>
       </c>
       <c r="F32" t="n">
-        <v>2.430681578740091</v>
+        <v>5.280945311348097</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08955799564679247</v>
+        <v>0.009581282719673867</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5373318625117014</v>
+        <v>-0.9182103561213713</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6773927509467408</v>
+        <v>-0.9366428919921828</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.791239752451141</v>
+        <v>-0.9783672453037161</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.115244324250646</v>
+        <v>-0.2159104521227844</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6827006151922415</v>
+        <v>-0.4095828708148088</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.002585258822989308</v>
+        <v>-0.0003349358401701086</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>52.20226745490961</v>
+        <v>53.59240369395961</v>
       </c>
       <c r="B33" t="n">
-        <v>68.48486684455166</v>
+        <v>103.8467494539726</v>
       </c>
       <c r="C33" t="n">
-        <v>38.78545897127647</v>
+        <v>38.62802516052095</v>
       </c>
       <c r="D33" t="n">
-        <v>7.107242191017444</v>
+        <v>6.788698472514536</v>
       </c>
       <c r="E33" t="n">
-        <v>4.271860243844224</v>
+        <v>4.3614299220002</v>
       </c>
       <c r="F33" t="n">
-        <v>3.436534370990952</v>
+        <v>3.532970729626869</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03264426501505729</v>
+        <v>0.02903979503011551</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7972621924465112</v>
+        <v>-0.7852113933421548</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8430413665760844</v>
+        <v>-0.83439241257414</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9294611456072454</v>
+        <v>-0.9239900818893273</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1653110930972485</v>
+        <v>-0.01149088424202202</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5994128513888551</v>
+        <v>-0.5894185567284109</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.001233617069661559</v>
+        <v>-0.01320587078822127</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>37.39253925307425</v>
+        <v>65.96106439307312</v>
       </c>
       <c r="B34" t="n">
-        <v>58.62955664483039</v>
+        <v>99.94381099532065</v>
       </c>
       <c r="C34" t="n">
-        <v>38.78263513803982</v>
+        <v>38.57221024110278</v>
       </c>
       <c r="D34" t="n">
-        <v>5.124471029588693</v>
+        <v>10.39478169761144</v>
       </c>
       <c r="E34" t="n">
-        <v>3.482956599783035</v>
+        <v>2.644570539004786</v>
       </c>
       <c r="F34" t="n">
-        <v>2.270589666242387</v>
+        <v>4.338434703721497</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1090258720129682</v>
+        <v>0.01496408224143037</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4601673709887121</v>
+        <v>-0.8812058990567361</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6333694574439207</v>
+        <v>-0.9056773230232164</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7439396382012979</v>
+        <v>-0.9647289478844051</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.05956181071210693</v>
+        <v>-0.01965897236672404</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6671452094880994</v>
+        <v>-0.3449725838006459</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0006583559617560047</v>
+        <v>-0.0001823895906490069</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>64.57666907377101</v>
+        <v>32.8162864759337</v>
       </c>
       <c r="B35" t="n">
-        <v>75.22954425453661</v>
+        <v>62.91792504783522</v>
       </c>
       <c r="C35" t="n">
-        <v>38.7805424061898</v>
+        <v>38.57242337529329</v>
       </c>
       <c r="D35" t="n">
-        <v>5.028966095210281</v>
+        <v>5.84957475129356</v>
       </c>
       <c r="E35" t="n">
-        <v>4.848375513398022</v>
+        <v>2.661727470498474</v>
       </c>
       <c r="F35" t="n">
-        <v>4.515126808007282</v>
+        <v>1.979444785990941</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01512567146097341</v>
+        <v>0.1766221331932346</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8912897343740103</v>
+        <v>-0.08892946548522462</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9148359672670686</v>
+        <v>-0.4408979048908073</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9689370003588792</v>
+        <v>-0.4887174697209578</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.07053474410925378</v>
+        <v>-0.01219100404315801</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.678793085251869</v>
+        <v>-0.6374742457127209</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0002320321877577127</v>
+        <v>-0.0002321209017684678</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>59.17402592782946</v>
+        <v>46.33242495630226</v>
       </c>
       <c r="B36" t="n">
-        <v>184.6473445091913</v>
+        <v>82.93023071882705</v>
       </c>
       <c r="C36" t="n">
-        <v>39.88777785304794</v>
+        <v>38.57420696799026</v>
       </c>
       <c r="D36" t="n">
-        <v>10.80141005974179</v>
+        <v>7.94969456661181</v>
       </c>
       <c r="E36" t="n">
-        <v>4.86620857997421</v>
+        <v>2.101670997652585</v>
       </c>
       <c r="F36" t="n">
-        <v>3.812708438548573</v>
+        <v>2.989168520343835</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02268882188332601</v>
+        <v>0.04996730036801218</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8571761717238301</v>
+        <v>-0.6695918823085721</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8865837264118172</v>
+        <v>-0.7569089497144461</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.954961708560116</v>
+        <v>-0.8656345224267115</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0646194136838328</v>
+        <v>-0.09887978127541674</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3170340998821849</v>
+        <v>-0.5434386913899143</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.09027598389834106</v>
+        <v>-0.0006482925310601073</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>81.18409274006726</v>
+        <v>98.4729779162423</v>
       </c>
       <c r="B37" t="n">
-        <v>140.908079553228</v>
+        <v>77.11899516164907</v>
       </c>
       <c r="C37" t="n">
-        <v>38.78610181795113</v>
+        <v>39.64496950961328</v>
       </c>
       <c r="D37" t="n">
-        <v>9.184149174688406</v>
+        <v>7.290296340102929</v>
       </c>
       <c r="E37" t="n">
-        <v>4.80447635477843</v>
+        <v>2.601390537289941</v>
       </c>
       <c r="F37" t="n">
-        <v>5.745542120659594</v>
+        <v>7.764778323924391</v>
       </c>
       <c r="G37" t="n">
-        <v>0.007395154864254999</v>
+        <v>0.003856966285488028</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9429965636642959</v>
+        <v>-0.9624799243877955</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9560265724995757</v>
+        <v>-0.9703804784934011</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.986501129241235</v>
+        <v>-0.9921717081699275</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1485361942659378</v>
+        <v>-0.1068962013166454</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4814508337302474</v>
+        <v>-0.5766199676532264</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.001364575472401839</v>
+        <v>-0.2504928855764328</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89.4078313693964</v>
+        <v>32.00582656360344</v>
       </c>
       <c r="B38" t="n">
-        <v>72.02863026746567</v>
+        <v>62.63011018869831</v>
       </c>
       <c r="C38" t="n">
-        <v>38.77974669174939</v>
+        <v>39.0037629392977</v>
       </c>
       <c r="D38" t="n">
-        <v>7.839772933640386</v>
+        <v>5.849585006547325</v>
       </c>
       <c r="E38" t="n">
-        <v>4.365026804145592</v>
+        <v>2.798165725536137</v>
       </c>
       <c r="F38" t="n">
-        <v>6.565680329167038</v>
+        <v>1.925501786218636</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005341056290611572</v>
+        <v>0.1945415254173263</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9567321221498681</v>
+        <v>-0.01843415337617534</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9660529961711719</v>
+        <v>-0.4070703890946749</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.990574391890063</v>
+        <v>-0.4355249762419502</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.07650920837251145</v>
+        <v>-0.02349650150808459</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5428827347321403</v>
+        <v>-0.6375364160225215</v>
       </c>
       <c r="M38" t="n">
-        <v>-6.993211590514322e-05</v>
+        <v>-0.1008780191694635</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>82.49411603699787</v>
+        <v>39.62918298609539</v>
       </c>
       <c r="B39" t="n">
-        <v>99.11508925056926</v>
+        <v>71.86051054786108</v>
       </c>
       <c r="C39" t="n">
-        <v>38.79355359170317</v>
+        <v>38.5848351270084</v>
       </c>
       <c r="D39" t="n">
-        <v>8.465301530570938</v>
+        <v>5.380247392241893</v>
       </c>
       <c r="E39" t="n">
-        <v>4.404676171758883</v>
+        <v>2.651651412223822</v>
       </c>
       <c r="F39" t="n">
-        <v>5.808458876013689</v>
+        <v>2.50409617602035</v>
       </c>
       <c r="G39" t="n">
-        <v>0.006977538280869635</v>
+        <v>0.08588046162049917</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9455978289788937</v>
+        <v>-0.4789914429337058</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9579252079765815</v>
+        <v>-0.6436927327101239</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9873057930711582</v>
+        <v>-0.7559350228093951</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.03170414077369528</v>
+        <v>-0.1324665210557863</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4912367991061655</v>
+        <v>-0.6727982739799414</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.002882623906997165</v>
+        <v>-0.003128196301960123</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>71.90886876820436</v>
+        <v>34.13479144471894</v>
       </c>
       <c r="B40" t="n">
-        <v>115.857811816992</v>
+        <v>61.42012617160303</v>
       </c>
       <c r="C40" t="n">
-        <v>38.78546747749949</v>
+        <v>40.3590110349611</v>
       </c>
       <c r="D40" t="n">
-        <v>10.15275546971329</v>
+        <v>5.618026358079186</v>
       </c>
       <c r="E40" t="n">
-        <v>4.906893429246014</v>
+        <v>2.852550343874562</v>
       </c>
       <c r="F40" t="n">
-        <v>4.867387800751038</v>
+        <v>2.086924706593106</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0112584282932129</v>
+        <v>0.1518895771719829</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9191171299371813</v>
+        <v>-0.189710790047669</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9375070748802921</v>
+        <v>-0.4905477839171355</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9786693146553102</v>
+        <v>-0.5623666922498705</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1382274403935576</v>
+        <v>-0.0360854686141067</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.4121642638996172</v>
+        <v>-0.6455088853662561</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.001235349926693818</v>
+        <v>-0.4171025748242566</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39.38928937321164</v>
+        <v>40.05584614068581</v>
       </c>
       <c r="B41" t="n">
-        <v>75.52199465407416</v>
+        <v>62.91738296729596</v>
       </c>
       <c r="C41" t="n">
-        <v>38.79209389036737</v>
+        <v>38.57264686874303</v>
       </c>
       <c r="D41" t="n">
-        <v>5.051916864724258</v>
+        <v>5.37287392761655</v>
       </c>
       <c r="E41" t="n">
-        <v>4.351573646099908</v>
+        <v>2.881719208797182</v>
       </c>
       <c r="F41" t="n">
-        <v>2.41830338846835</v>
+        <v>2.543047442495487</v>
       </c>
       <c r="G41" t="n">
-        <v>0.08961524451062511</v>
+        <v>0.0824828716811002</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5372829461446121</v>
+        <v>-0.4952838460325704</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6773524851609226</v>
+        <v>-0.652936175768127</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7911943168449245</v>
+        <v>-0.7659918966812236</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06064791715344577</v>
+        <v>-0.1513567503275838</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6770113854426182</v>
+        <v>-0.675331586460322</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.002585258822989308</v>
+        <v>-0.0002842693733731694</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>92.40459295112893</v>
+        <v>34.00790046003458</v>
       </c>
       <c r="B42" t="n">
-        <v>173.2938145703371</v>
+        <v>60.09369718189579</v>
       </c>
       <c r="C42" t="n">
-        <v>38.79067544271232</v>
+        <v>38.57392922669992</v>
       </c>
       <c r="D42" t="n">
-        <v>7.288805367912135</v>
+        <v>5.618026358079186</v>
       </c>
       <c r="E42" t="n">
-        <v>2.382344896353437</v>
+        <v>2.223363393830844</v>
       </c>
       <c r="F42" t="n">
-        <v>6.881000589304582</v>
+        <v>2.045147855618892</v>
       </c>
       <c r="G42" t="n">
-        <v>0.004790645344339917</v>
+        <v>0.1537918095616773</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.9605934714196451</v>
+        <v>-0.1808528834225376</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9689731284589044</v>
+        <v>-0.4861449404744305</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9916520305554499</v>
+        <v>-0.5560837658623818</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.0351716676171606</v>
+        <v>-0.0270707565285744</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5652687527116886</v>
+        <v>-0.6500493778752161</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.002296297789823887</v>
+        <v>-0.0005834862299805565</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>31.44651464713573</v>
+        <v>43.30610532271182</v>
       </c>
       <c r="B43" t="n">
-        <v>68.83274527158565</v>
+        <v>83.87906961957461</v>
       </c>
       <c r="C43" t="n">
-        <v>38.77981257031102</v>
+        <v>38.57271341777925</v>
       </c>
       <c r="D43" t="n">
-        <v>5.909294457696696</v>
+        <v>7.869852272341859</v>
       </c>
       <c r="E43" t="n">
-        <v>4.534128968093808</v>
+        <v>2.099557540281056</v>
       </c>
       <c r="F43" t="n">
-        <v>1.877565929046194</v>
+        <v>2.723759440445338</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2127690933628111</v>
+        <v>0.06426219441481455</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0958413490732805</v>
+        <v>-0.5965290715855156</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.444261885048702</v>
+        <v>-0.7115972107867564</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4922125396631255</v>
+        <v>-0.8250076427316378</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.007962571488459967</v>
+        <v>-0.004378907817429434</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6332563809814123</v>
+        <v>-0.5242720003771748</v>
       </c>
       <c r="M43" t="n">
-        <v>-8.335265854086208e-05</v>
+        <v>-0.0002997974818240434</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>90.39130077051664</v>
+        <v>63.44152796790824</v>
       </c>
       <c r="B44" t="n">
-        <v>90.21849225286864</v>
+        <v>100.3330159391831</v>
       </c>
       <c r="C44" t="n">
-        <v>38.78252654603478</v>
+        <v>38.57271384863652</v>
       </c>
       <c r="D44" t="n">
-        <v>7.839772933640386</v>
+        <v>10.41029020519925</v>
       </c>
       <c r="E44" t="n">
-        <v>4.365026804145592</v>
+        <v>2.897484673124308</v>
       </c>
       <c r="F44" t="n">
-        <v>6.689823246932605</v>
+        <v>4.109875300549055</v>
       </c>
       <c r="G44" t="n">
-        <v>0.00515605839860237</v>
+        <v>0.01718491172131161</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.9580458784893948</v>
+        <v>-0.8684198337077922</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.9670307825300661</v>
+        <v>-0.8961042229004248</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9909432851966211</v>
+        <v>-0.9599871547176726</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.1058102091551517</v>
+        <v>-0.008793824159016183</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5502293197357712</v>
+        <v>-0.338916173265329</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0006362339907005475</v>
+        <v>-0.0002998980151878994</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31.67844952088827</v>
+        <v>37.00262566066482</v>
       </c>
       <c r="B45" t="n">
-        <v>72.55982587437218</v>
+        <v>57.97703062249749</v>
       </c>
       <c r="C45" t="n">
-        <v>38.78128833985093</v>
+        <v>38.58448150464958</v>
       </c>
       <c r="D45" t="n">
-        <v>5.940830373622886</v>
+        <v>5.391653245734425</v>
       </c>
       <c r="E45" t="n">
-        <v>3.633191497474477</v>
+        <v>4.357562635271361</v>
       </c>
       <c r="F45" t="n">
-        <v>1.898563666416827</v>
+        <v>2.268351596204161</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2068739885533427</v>
+        <v>0.1113127834800659</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.115376924363416</v>
+        <v>-0.3627469873411807</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4537751536185013</v>
+        <v>-0.5800754723254663</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5067084670252553</v>
+        <v>-0.68185066634067</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.0284823040503189</v>
+        <v>-0.05326884713831662</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6347001890478592</v>
+        <v>-0.5939002248947369</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0003839910990556648</v>
+        <v>-0.003045684418236105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>43.37090933847581</v>
+        <v>56.68422672611064</v>
       </c>
       <c r="B46" t="n">
-        <v>71.50576173222008</v>
+        <v>113.2824350298291</v>
       </c>
       <c r="C46" t="n">
-        <v>38.78221181840887</v>
+        <v>39.5926077846423</v>
       </c>
       <c r="D46" t="n">
-        <v>5.034425623238298</v>
+        <v>11.49747551381543</v>
       </c>
       <c r="E46" t="n">
-        <v>4.706056237667741</v>
+        <v>4.090838635103147</v>
       </c>
       <c r="F46" t="n">
-        <v>2.79864975358151</v>
+        <v>3.705135028678807</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0624571969071778</v>
+        <v>0.02618015186080383</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6520179710720296</v>
+        <v>-0.8143132140559912</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7465990966244279</v>
+        <v>-0.8540235766150418</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.856761527315361</v>
+        <v>-0.9363697456845511</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.2931407543573892</v>
+        <v>-0.09833419437553093</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.7018538858923674</v>
+        <v>-0.2788751154235383</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0005721188154769426</v>
+        <v>-0.2382751497498713</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40.83614974247347</v>
+        <v>77.44761894772756</v>
       </c>
       <c r="B47" t="n">
-        <v>65.62705038840167</v>
+        <v>113.3799383638568</v>
       </c>
       <c r="C47" t="n">
-        <v>38.77971073030798</v>
+        <v>38.57196134786753</v>
       </c>
       <c r="D47" t="n">
-        <v>5.108871862216018</v>
+        <v>9.672464833859973</v>
       </c>
       <c r="E47" t="n">
-        <v>4.630958532518545</v>
+        <v>2.249799736861589</v>
       </c>
       <c r="F47" t="n">
-        <v>2.57360426268797</v>
+        <v>5.41505156903854</v>
       </c>
       <c r="G47" t="n">
-        <v>0.07821995712721176</v>
+        <v>0.008533381880106506</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5841895393933977</v>
+        <v>-0.9254943137239843</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7050593813054699</v>
+        <v>-0.9431048735402924</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.818738278740878</v>
+        <v>-0.9808734035362452</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.219992769660931</v>
+        <v>-0.08380725979873958</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.691707405065469</v>
+        <v>-0.4268142850025589</v>
       </c>
       <c r="M47" t="n">
-        <v>-6.26061809440535e-05</v>
+        <v>-0.0001243145024230896</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>87.62752470139975</v>
+        <v>78.59295713452752</v>
       </c>
       <c r="B48" t="n">
-        <v>155.7545864160596</v>
+        <v>83.87906961957461</v>
       </c>
       <c r="C48" t="n">
-        <v>38.78661731322555</v>
+        <v>38.57281352695829</v>
       </c>
       <c r="D48" t="n">
-        <v>7.782913277019459</v>
+        <v>9.665003392138955</v>
       </c>
       <c r="E48" t="n">
-        <v>4.362278946887389</v>
+        <v>2.101670997652585</v>
       </c>
       <c r="F48" t="n">
-        <v>6.337759272511513</v>
+        <v>5.540500115578372</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005698652594353576</v>
+        <v>0.008120022579568304</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.9542069412769243</v>
+        <v>-0.9285769885401293</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9641923784087526</v>
+        <v>-0.9458349996454799</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9898560594794941</v>
+        <v>-0.9819002700361901</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.009457039125588908</v>
+        <v>-0.1039421762335329</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5295837197815275</v>
+        <v>-0.4349748195835086</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.001469590307851511</v>
+        <v>-0.0003231562902686336</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>75.00464502234018</v>
+        <v>63.56298328961562</v>
       </c>
       <c r="B49" t="n">
-        <v>136.6776309691084</v>
+        <v>100.3330159391831</v>
       </c>
       <c r="C49" t="n">
-        <v>38.78610181795113</v>
+        <v>38.57281395781556</v>
       </c>
       <c r="D49" t="n">
-        <v>9.14724434936895</v>
+        <v>10.47689857367905</v>
       </c>
       <c r="E49" t="n">
-        <v>4.797331349413403</v>
+        <v>2.89999249097344</v>
       </c>
       <c r="F49" t="n">
-        <v>5.063812992562472</v>
+        <v>4.12887534502572</v>
       </c>
       <c r="G49" t="n">
-        <v>0.009660404188355039</v>
+        <v>0.01707903667146401</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.9284891944260255</v>
+        <v>-0.869143094316036</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9454522895487735</v>
+        <v>-0.8966716602626379</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9818607963016619</v>
+        <v>-0.9602737619328001</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.006553392239364934</v>
+        <v>-0.02332621670559528</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4352899283863053</v>
+        <v>-0.3398043153053142</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.001364575472401839</v>
+        <v>-0.000323256823630963</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>76.34613931475177</v>
+        <v>55.92750903652153</v>
       </c>
       <c r="B50" t="n">
-        <v>140.908079553228</v>
+        <v>102.2430384554667</v>
       </c>
       <c r="C50" t="n">
-        <v>38.78610181795113</v>
+        <v>38.57244029767573</v>
       </c>
       <c r="D50" t="n">
-        <v>9.184149174688406</v>
+        <v>7.122388678890653</v>
       </c>
       <c r="E50" t="n">
-        <v>4.797331349413403</v>
+        <v>2.98796255724322</v>
       </c>
       <c r="F50" t="n">
-        <v>5.210781863603983</v>
+        <v>3.813356278423997</v>
       </c>
       <c r="G50" t="n">
-        <v>0.009096755948263311</v>
+        <v>0.02495152790135385</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.9320358328942501</v>
+        <v>-0.8104190653851293</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9481960022735656</v>
+        <v>-0.8524403853303683</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9830250009790665</v>
+        <v>-0.9354964052578343</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.0436072805496345</v>
+        <v>-0.172183834543457</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.4453109842929369</v>
+        <v>-0.604207557231303</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.001364575472401839</v>
+        <v>-0.0002360694576684919</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>70.32172659135433</v>
+        <v>33.58642552669675</v>
       </c>
       <c r="B51" t="n">
-        <v>125.1118408854507</v>
+        <v>60.87285636279328</v>
       </c>
       <c r="C51" t="n">
-        <v>39.03074660958502</v>
+        <v>38.57219887980479</v>
       </c>
       <c r="D51" t="n">
-        <v>9.709175826699758</v>
+        <v>5.618026358079186</v>
       </c>
       <c r="E51" t="n">
-        <v>4.763093781489776</v>
+        <v>2.615392539550291</v>
       </c>
       <c r="F51" t="n">
-        <v>4.662348150856207</v>
+        <v>2.011554051660978</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01212658240579898</v>
+        <v>0.1613158729504993</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9137874497459509</v>
+        <v>-0.1498817078064807</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9329304980288897</v>
+        <v>-0.4707585333547054</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9768227999619764</v>
+        <v>-0.5336783643780524</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.03310065227147507</v>
+        <v>-0.006533406047840252</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4003082011672182</v>
+        <v>-0.6474151595418547</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.05095607516587444</v>
+        <v>-0.0001797386211176144</v>
       </c>
     </row>
   </sheetData>
